--- a/pandemic-loss-modeling/exceedance_results/marani_inspired_1901.xlsx
+++ b/pandemic-loss-modeling/exceedance_results/marani_inspired_1901.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -390,7 +390,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
         <v>0.1</v>
@@ -398,81 +398,73 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.002</v>
+        <v>7.2</v>
       </c>
       <c r="B3">
-        <v>0.1</v>
+        <v>0.04503991703205042</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>0.04503991703205042</v>
+        <v>0.02075035276239215</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B5">
-        <v>0.02075035276239215</v>
+        <v>0.01521898618032487</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="B6">
-        <v>0.01521898618032487</v>
+        <v>0.009799323140329642</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="B7">
-        <v>0.009799323140329642</v>
+        <v>0.006650020538879831</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="B8">
-        <v>0.006650020538879831</v>
+        <v>0.005430140242982284</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B9">
-        <v>0.005430140242982284</v>
+        <v>0.005076318278307701</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="B10">
-        <v>0.005076318278307701</v>
+        <v>0.004636954874857191</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B11">
-        <v>0.004636954874857191</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>280</v>
-      </c>
-      <c r="B12">
         <v>0.004278771071997256</v>
       </c>
     </row>
